--- a/관심종목/09_SW_구간표준.xlsx
+++ b/관심종목/09_SW_구간표준.xlsx
@@ -14,7 +14,7 @@
     <sheet name="종목 목록" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'종목 목록'!$A$1:$I$78</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'종목 목록'!$A$1:$I$86</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="347">
   <si>
     <r>
       <rPr>
@@ -443,19 +443,11 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">소프트웨어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SaaS IT</t>
     </r>
     <r>
       <rPr>
@@ -897,6 +889,219 @@
     <t xml:space="preserve">트렌드마이크로</t>
   </si>
   <si>
+    <t xml:space="preserve">양자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아이씨티케이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옵티시스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리넷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">코위버</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쏠리드</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아이온큐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SQ, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리게티 컴퓨팅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, DEFIANCE QUANTUM, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디웨이브 퀀텀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">퀀텀 컴퓨팅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알고리듬 홀딩스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인플렉션</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
     <t xml:space="preserve">게임</t>
   </si>
   <si>
@@ -1300,11 +1505,287 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sw / </t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미국 헬스케어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구간없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">서비스나우</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09 SW·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보안 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ SaaS IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서비스</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">워크데이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">세일스포스</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미국 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">new / SPACE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">인튜이트</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미국 정책 수혜주 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보안</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">데이터도그</t>
+  </si>
+  <si>
+    <t xml:space="preserve">크라우드스트라이크 홀딩스</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09 SW·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보안 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보안</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">팰로 앨토 네트웍스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">옥타</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미국 데이터센터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자컴퓨터</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">아이온큐</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09 SW·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보안 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
     </r>
     <r>
       <rPr>
@@ -1316,25 +1797,67 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">아이씨티케이</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SQ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">리게티 컴퓨팅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEFIANCE QUANTUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">디웨이브 퀀텀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">퀀텀 컴퓨팅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">알고리듬 홀딩스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인플렉션</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일본 테마 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구간없음</t>
     </r>
     <r>
       <rPr>
@@ -1347,45 +1870,289 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">옵티시스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">우리넷</t>
+    <t xml:space="preserve">NEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">후지쯔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결정이 필요한 항목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현재 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">검토 내용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추천</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결정 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접 입력</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">한국정보통신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보안 구간에 유지</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 단말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(VAN) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업체</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금융 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 핀테크로 이동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">더존비즈온</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">키움 조회에서 종목 정보 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상장 여부 확인 후 추가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자율주행 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종목</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">탭 밖 이동</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현대오토에버</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">슈어소프트테크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모트렉스</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동차 정리 때 반영</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">우리로</t>
   </si>
   <si>
-    <t xml:space="preserve">코위버</t>
-  </si>
-  <si>
-    <t xml:space="preserve">쏠리드</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미국 헬스케어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구간없음</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 구간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터센터 탭과 중복</t>
     </r>
     <r>
       <rPr>
@@ -1398,25 +2165,188 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">서비스나우</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">09 SW·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게임</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포토다이오드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광부품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자암호</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">의도적 중복 유지 또는 한 곳만 선택</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">후지쯔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·NEC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SaaS IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서비스 구간</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본업 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SI, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자컴퓨터 개발</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메모로 양자 표시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 탭이라 함께 보임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소프트뱅크그룹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스퀘어</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일장</t>
     </r>
     <r>
       <rPr>
@@ -1433,647 +2363,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">보안 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">소프트웨어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서비스</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">워크데이</t>
-  </si>
-  <si>
-    <t xml:space="preserve">세일스포스</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미국 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">new / SPACE</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">인튜이트</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미국 정책 수혜주 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보안</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">데이터도그</t>
-  </si>
-  <si>
-    <t xml:space="preserve">크라우드스트라이크 홀딩스</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">09 SW·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보안 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보안</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">팰로 앨토 네트웍스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">옥타</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일본 테마 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구간없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">후지쯔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">결정이 필요한 항목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">항목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현재 처리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">검토 내용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추천</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결정 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직접 입력</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">한국정보통신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보안 구간에 유지</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 단말</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(VAN) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">업체</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 핀테크로 이동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">더존비즈온</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미추가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">키움 조회에서 종목 정보 없음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상장 여부 확인 후 추가</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자율주행 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종목</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">탭 밖 이동</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현대오토에버</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">슈어소프트테크</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모트렉스</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">05 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로봇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자동차 정리 때 반영</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종목</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아이씨티케이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">옵티시스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">우리넷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">우리로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">코위버</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">쏠리드</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자 정리 때 반영</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">소프트뱅크그룹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스퀘어</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">국장</t>
     </r>
   </si>
@@ -2097,57 +2386,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">투자형 지주사 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(ARM·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오픈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI / SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하이닉스 지분</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">투자형 지주사</t>
   </si>
   <si>
     <r>
@@ -2499,7 +2738,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">빈칸메모 입력 순서 </t>
+      <t xml:space="preserve">빈칸메모 입력 순서</t>
     </r>
     <r>
       <rPr>
@@ -2509,7 +2748,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -2518,7 +2757,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">세 시장 공통</t>
+      <t xml:space="preserve">플랫폼 </t>
     </r>
     <r>
       <rPr>
@@ -2528,7 +2767,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">): </t>
+      <t xml:space="preserve">/ SaaS IT</t>
     </r>
     <r>
       <rPr>
@@ -2537,7 +2776,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">플랫폼 </t>
+      <t xml:space="preserve">서비스 </t>
     </r>
     <r>
       <rPr>
@@ -2547,7 +2786,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/ </t>
+      <t xml:space="preserve">/ AI </t>
     </r>
     <r>
       <rPr>
@@ -2566,7 +2805,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">IT</t>
+      <t xml:space="preserve">/ </t>
     </r>
     <r>
       <rPr>
@@ -2575,7 +2814,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">서비스 </t>
+      <t xml:space="preserve">보안 </t>
     </r>
     <r>
       <rPr>
@@ -2585,7 +2824,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/ AI </t>
+      <t xml:space="preserve">/ </t>
     </r>
     <r>
       <rPr>
@@ -2594,7 +2833,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">소프트웨어 </t>
+      <t xml:space="preserve">양자 </t>
     </r>
     <r>
       <rPr>
@@ -2613,7 +2852,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">보안 </t>
+      <t xml:space="preserve">게임 </t>
     </r>
     <r>
       <rPr>
@@ -2623,7 +2862,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/ </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -2632,28 +2871,784 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">일장은 양자 구간 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">구간 순서</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원래 위치 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탭 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구간</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종목코드</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">티커</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">영웅문 코드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메모</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">035420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구간 이동</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금융 탭에서 빼고 여기로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구글</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메타 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">카카오</t>
+  </si>
+  <si>
+    <t xml:space="preserve">035720</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신규 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신규</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사람인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">신규</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구인 플랫폼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리크루트 짝</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sw / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보안</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">삼성에스디에스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">018260</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서비스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">가비아</t>
+  </si>
+  <si>
+    <t xml:space="preserve">079940</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">호스팅</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">케이아이엔엑스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">093320</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인터넷 연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(IX), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가비아 자회사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">솔트룩스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304100</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">언어모델</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팔란티어 테마 연동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">코난테크놀로지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402030</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">언어모델</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">윈스테크넷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안랩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">053800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엑스게이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">025770</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VAN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업체</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">150900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에스투더블유</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">드림시큐리티</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라온시큐어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">042510</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sw / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">아이씨티케이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">456010</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자암호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자통신</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">옵티시스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">우리넷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">046970</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자암호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터센터 탭 광부품과 중복</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">코위버</t>
+  </si>
+  <si>
+    <t xml:space="preserve">056360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">쏠리드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">050890</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sw / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">게임</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">구간 순서</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원래 위치 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+    <t xml:space="preserve">NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">036570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">크래프톤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">259960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">펄어비스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위메이드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">컴투스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">078340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">넷마블</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">넥슨게임즈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225570</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">넥슨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2662,19 +3657,158 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탭 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일본 상장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개발 자회사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">060250</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금융</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핀테크로 이동 완료</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">234340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">064260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">054920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">064400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">053300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">041190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">462860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307950</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동차 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2683,19 +3817,170 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구간</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자율주행으로 이동 예정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">298830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118990</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월가 포트폴리오 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">드러켄밀러</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">아마존닷컴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMZN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDAMZN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월가 탭과 의도적 중복</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마이크로소프트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDMSFT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">애저 클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빅테크</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알파벳 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDGOOGL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAVER </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">짝</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메타 플랫폼스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">페이스북</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2704,64 +3989,429 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종목코드</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">티커</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">영웅문 코드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상태</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메모</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAVER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">035420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구간 이동</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융 탭에서 빼고 여기로 </t>
+    <t xml:space="preserve">META</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDMETA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카카오 짝</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미국 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sw / SaaS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">브로드리지 파이낸셜 솔루션</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYBR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금융 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SW</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">피그마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYFIG</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디자인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SaaS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYNOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">헬스케어 탭에서 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDWDAY</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">헬스케어 탭에서 이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, HR SaaS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYCRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDINTU</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">new </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탭에서 이동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DDOG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDDDOG</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모니터링 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SW, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정책 수혜주 탭에서 이동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">오라클</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYORCL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터센터 수요</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">팔란티어 테크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDPLTR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI SW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">테마 선행 신호</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CRWD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDCRWD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정책 수혜주 탭에서 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDPANW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDOKTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IONQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYIONQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">데이터센터 탭에서 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDLAES</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자내성 보안칩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국장 양자암호 짝</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RGTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRGTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QTUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDQTUM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ETF</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">QBTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDQBTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDQUBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYINFQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로블록스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBLX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYRBLX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">테이크 투 인터랙티브 소프트웨어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTWO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDTTWO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크래프톤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">펄어비스 짝 </t>
     </r>
     <r>
       <rPr>
@@ -2778,24 +4428,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구글</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메타 짝</t>
+      <t xml:space="preserve">콘솔 대작</t>
     </r>
     <r>
       <rPr>
@@ -2808,36 +4441,242 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">카카오</t>
-  </si>
-  <si>
-    <t xml:space="preserve">035720</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신규 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신규</t>
+    <t xml:space="preserve">리크루트홀딩스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06098</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인디드 운영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사람인 짝</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">코퍼레이션</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">04689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04689</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라인야후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, NAVER·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카카오 짝</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">06701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06701</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일본 테마 탭에서 이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">삼성에스디에스 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자컴퓨터 개발 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 구간 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">해저케이블</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">06702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06702</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일본 테마 탭에서 이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">삼성에스디에스 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자컴퓨터 개발 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 구간 짝</t>
     </r>
     <r>
       <rPr>
@@ -2847,1362 +4686,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">사람인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">신규</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구인 플랫폼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">리크루트 짝</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sw / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보안</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">삼성에스디에스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">018260</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서비스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">가비아</t>
-  </si>
-  <si>
-    <t xml:space="preserve">079940</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">호스팅</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">케이아이엔엑스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">093320</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인터넷 연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(IX), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가비아 자회사</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">솔트룩스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304100</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">언어모델</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">팔란티어 테마 연동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">코난테크놀로지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402030</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">검색</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">언어모델</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">윈스테크넷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">유지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">안랩</t>
-  </si>
-  <si>
-    <t xml:space="preserve">053800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엑스게이트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">025770</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VAN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">업체</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">150900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">에스투더블유</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">드림시큐리티</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">라온시큐어</t>
-  </si>
-  <si>
-    <t xml:space="preserve">042510</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sw / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게임</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">036570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">크래프톤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">259960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">펄어비스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">위메이드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">컴투스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">078340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">넷마블</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">넥슨게임즈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225570</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">넥슨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일본 상장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개발 자회사</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">060250</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">핀테크로 이동 완료</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">234340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">064260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">054920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">064400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">053300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">041190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">462860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307950</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">05 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로봇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자동차 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자율주행으로 이동 예정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">298830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">456010</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자로 이동 예정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">109080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">046970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">056360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">050890</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">월가 포트폴리오 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">드러켄밀러</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">아마존닷컴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDAMZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">월가 탭과 의도적 중복</t>
-  </si>
-  <si>
-    <t xml:space="preserve">마이크로소프트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSFT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDMSFT</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">애저 클라우드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빅테크</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알파벳 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">GOOGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDGOOGL</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAVER </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">짝</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메타 플랫폼스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">페이스북</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">META</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDMETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">카카오 짝</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미국 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sw / SaaS</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">브로드리지 파이낸셜 솔루션</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYBR</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SW</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">피그마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYFIG</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디자인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SaaS</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYNOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">헬스케어 탭에서 이동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDWDAY</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">헬스케어 탭에서 이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, HR SaaS</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYCRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDINTU</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">new </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탭에서 이동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">DDOG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDDDOG</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모니터링 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SW, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정책 수혜주 탭에서 이동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">오라클</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYORCL</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터센터 수요</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">팔란티어 테크</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLTR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDPLTR</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">국장 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI SW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">테마 선행 신호</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CRWD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDCRWD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정책 수혜주 탭에서 이동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDPANW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OKTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDOKTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">로블록스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBLX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYRBLX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">테이크 투 인터랙티브 소프트웨어</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTWO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDTTWO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">크래프톤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">펄어비스 짝 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">콘솔 대작</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">리크루트홀딩스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06098</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인디드 운영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사람인 짝</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">코퍼레이션</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">04689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W04689</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">라인야후</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, NAVER·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카카오 짝</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">06701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06701</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일본 테마 탭에서 이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">삼성에스디에스 짝 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">해저케이블도 함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">06702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06702</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일본 테마 탭에서 이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">삼성에스디에스 짝</t>
     </r>
   </si>
   <si>
@@ -4905,7 +5388,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -4960,15 +5443,15 @@
         <v>10</v>
       </c>
       <c r="C5" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"국장",'종목 목록'!$C$2:$C$78,$B5,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B5,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"미장",'종목 목록'!$C$2:$C$78,$B5,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B5,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"일장",'종목 목록'!$C$2:$C$78,$B5,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B5,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -4985,19 +5468,19 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"국장",'종목 목록'!$C$2:$C$78,$B6,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B6,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"미장",'종목 목록'!$C$2:$C$78,$B6,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B6,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"일장",'종목 목록'!$C$2:$C$78,$B6,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B6,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -5018,15 +5501,15 @@
         <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"국장",'종목 목록'!$C$2:$C$78,$B7,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B7,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"미장",'종목 목록'!$C$2:$C$78,$B7,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B7,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"일장",'종목 목록'!$C$2:$C$78,$B7,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B7,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -5047,15 +5530,15 @@
         <v>22</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"국장",'종목 목록'!$C$2:$C$78,$B8,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B8,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"미장",'종목 목록'!$C$2:$C$78,$B8,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B8,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"일장",'종목 목록'!$C$2:$C$78,$B8,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B8,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
         <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -5068,7 +5551,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
@@ -5076,41 +5559,70 @@
         <v>26</v>
       </c>
       <c r="C9" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"국장",'종목 목록'!$C$2:$C$78,$B9,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B9,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"미장",'종목 목록'!$C$2:$C$78,$B9,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B9,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <v>8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$78,"일장",'종목 목록'!$C$2:$C$78,$B9,'종목 목록'!$H$2:$H$78,"&lt;&gt;탭 밖 이동")</f>
-        <v>4</v>
-      </c>
-      <c r="F9" s="6" t="s">
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B9,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="9" t="s">
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <f aca="false">SUM(C5:C9)</f>
-        <v>23</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <f aca="false">SUM(D5:D9)</f>
-        <v>18</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <f aca="false">SUM(E5:E9)</f>
+      <c r="C10" s="4" t="n">
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B10,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B10,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B10,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <v>4</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <f aca="false">SUM(C5:C10)</f>
+        <v>29</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <f aca="false">SUM(D5:D10)</f>
+        <v>26</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <f aca="false">SUM(E5:E10)</f>
         <v>10</v>
       </c>
     </row>
@@ -5130,7 +5642,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -5141,21 +5653,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5163,13 +5675,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5177,13 +5689,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5191,13 +5703,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5205,13 +5717,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5219,13 +5731,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5233,13 +5745,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5247,13 +5759,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5261,13 +5773,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5275,13 +5787,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,13 +5801,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5303,13 +5815,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5317,13 +5829,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5331,13 +5843,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5345,13 +5857,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5359,13 +5871,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5373,13 +5885,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5387,13 +5899,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5401,13 +5913,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5415,13 +5927,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5429,97 +5941,97 @@
         <v>4</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>60</v>
+        <v>5</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>60</v>
+        <v>5</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>60</v>
+        <v>5</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>60</v>
+        <v>5</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>60</v>
+        <v>5</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="C28" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>60</v>
+        <v>5</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5527,13 +6039,13 @@
         <v>5</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5541,13 +6053,13 @@
         <v>5</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5555,13 +6067,13 @@
         <v>5</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5569,13 +6081,13 @@
         <v>5</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5583,13 +6095,13 @@
         <v>5</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5597,13 +6109,13 @@
         <v>5</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="13" t="s">
         <v>77</v>
       </c>
+      <c r="C35" s="14" t="s">
+        <v>82</v>
+      </c>
       <c r="D35" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5611,13 +6123,13 @@
         <v>5</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C36" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="14" t="s">
         <v>79</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5625,41 +6137,69 @@
         <v>5</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>70</v>
+      <c r="B40" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -5678,171 +6218,189 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="F7" s="15"/>
     </row>
-    <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="F8" s="15"/>
     </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F9" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="F10" s="15"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>118</v>
+      <c r="C11" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -5861,7 +6419,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -5876,31 +6434,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5914,22 +6472,22 @@
         <v>10</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5943,22 +6501,22 @@
         <v>10</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5972,22 +6530,22 @@
         <v>10</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5997,26 +6555,26 @@
       <c r="B5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F5" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>127</v>
-      </c>
       <c r="I5" s="19" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6026,26 +6584,26 @@
       <c r="B6" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6055,26 +6613,26 @@
       <c r="B7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6088,22 +6646,22 @@
         <v>18</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6117,22 +6675,22 @@
         <v>18</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6146,19 +6704,19 @@
         <v>22</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I10" s="19"/>
     </row>
@@ -6173,19 +6731,19 @@
         <v>22</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I11" s="19"/>
     </row>
@@ -6200,19 +6758,19 @@
         <v>22</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I12" s="19"/>
     </row>
@@ -6227,22 +6785,22 @@
         <v>22</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6256,19 +6814,19 @@
         <v>22</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I14" s="19"/>
     </row>
@@ -6283,19 +6841,19 @@
         <v>22</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I15" s="19"/>
     </row>
@@ -6310,19 +6868,19 @@
         <v>22</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E16" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>165</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>154</v>
       </c>
       <c r="I16" s="19"/>
     </row>
@@ -6337,19 +6895,19 @@
         <v>22</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I17" s="19"/>
     </row>
@@ -6364,21 +6922,23 @@
         <v>26</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>170</v>
+        <v>180</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>181</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I18" s="19"/>
+        <v>165</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
@@ -6391,21 +6951,23 @@
         <v>26</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I19" s="19"/>
+        <v>165</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
@@ -6418,21 +6980,23 @@
         <v>26</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="19"/>
+        <v>165</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
@@ -6445,21 +7009,23 @@
         <v>26</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I21" s="19"/>
+        <v>165</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
@@ -6472,21 +7038,23 @@
         <v>26</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I22" s="19"/>
+        <v>165</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
@@ -6499,211 +7067,213 @@
         <v>26</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="19"/>
+        <v>165</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
         <v>4</v>
       </c>
       <c r="B24" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>182</v>
+        <v>30</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>195</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>184</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="19" t="s">
-        <v>38</v>
+      <c r="B25" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>37</v>
+        <v>194</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>197</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>186</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="I25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="19" t="s">
-        <v>38</v>
+      <c r="B26" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="I26" s="19" t="s">
-        <v>186</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="I26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="19" t="s">
-        <v>38</v>
+      <c r="B27" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>186</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="I27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19" t="s">
-        <v>38</v>
+      <c r="B28" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>41</v>
+        <v>203</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" s="19" t="s">
-        <v>186</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="I28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19" t="s">
-        <v>38</v>
+      <c r="B29" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>186</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="I29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>36</v>
+      <c r="B30" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>142</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>186</v>
+        <v>145</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6712,25 +7282,25 @@
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>44</v>
+        <v>40</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>41</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I31" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6739,25 +7309,25 @@
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6766,25 +7336,25 @@
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6793,25 +7363,25 @@
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>47</v>
+        <v>40</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6820,25 +7390,25 @@
       </c>
       <c r="B35" s="18"/>
       <c r="C35" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6847,25 +7417,25 @@
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6874,25 +7444,25 @@
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6901,25 +7471,25 @@
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6928,25 +7498,25 @@
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6955,25 +7525,25 @@
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>53</v>
+        <v>40</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6982,25 +7552,25 @@
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7009,25 +7579,25 @@
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="19" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7036,25 +7606,25 @@
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="19" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7063,25 +7633,25 @@
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="19" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D44" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="17" t="s">
-        <v>59</v>
-      </c>
       <c r="F44" s="20" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7090,25 +7660,25 @@
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="19" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7117,25 +7687,25 @@
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="19" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7144,25 +7714,25 @@
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="19" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7171,25 +7741,25 @@
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D48" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E48" s="17" t="s">
-        <v>65</v>
-      </c>
       <c r="F48" s="20" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7198,25 +7768,25 @@
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>66</v>
-      </c>
       <c r="F49" s="20" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7225,25 +7795,25 @@
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7257,22 +7827,22 @@
         <v>10</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7286,22 +7856,22 @@
         <v>10</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7315,22 +7885,22 @@
         <v>10</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7344,22 +7914,22 @@
         <v>10</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7369,26 +7939,26 @@
       <c r="B55" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I55" s="17" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7398,26 +7968,26 @@
       <c r="B56" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7427,26 +7997,26 @@
       <c r="B57" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7456,26 +8026,26 @@
       <c r="B58" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="G58" s="20" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7485,26 +8055,26 @@
       <c r="B59" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D59" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E59" s="17" t="s">
-        <v>72</v>
-      </c>
       <c r="F59" s="20" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7514,26 +8084,26 @@
       <c r="B60" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I60" s="19" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7543,26 +8113,26 @@
       <c r="B61" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7576,22 +8146,22 @@
         <v>18</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7605,22 +8175,22 @@
         <v>18</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7634,22 +8204,22 @@
         <v>22</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7663,22 +8233,22 @@
         <v>22</v>
       </c>
       <c r="D65" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E65" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E65" s="17" t="s">
-        <v>79</v>
-      </c>
       <c r="F65" s="20" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7692,22 +8262,22 @@
         <v>22</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="G66" s="20" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7721,21 +8291,23 @@
         <v>26</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="I67" s="19"/>
+        <v>236</v>
+      </c>
+      <c r="I67" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="17" t="s">
@@ -7748,135 +8320,135 @@
         <v>26</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>134</v>
+        <v>236</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B69" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>134</v>
+        <v>236</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B70" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>134</v>
+        <v>236</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B71" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="H71" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B72" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I72" s="17" t="s">
         <v>290</v>
@@ -7884,175 +8456,405 @@
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B73" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>18</v>
+        <v>5</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="I73" s="19" t="s">
-        <v>293</v>
+        <v>236</v>
+      </c>
+      <c r="I73" s="17" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B74" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="G74" s="20" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>134</v>
+        <v>236</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="18" t="n">
-        <v>5</v>
-      </c>
       <c r="C75" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I75" s="19"/>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="18" t="n">
-        <v>5</v>
-      </c>
       <c r="C76" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="I76" s="19"/>
+        <v>145</v>
+      </c>
+      <c r="I76" s="17" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B77" s="18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="I77" s="19"/>
+        <v>145</v>
+      </c>
+      <c r="I77" s="17" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B78" s="18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E78" s="17" t="s">
-        <v>306</v>
+        <v>142</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>318</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="G78" s="20" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>309</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F79" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="G79" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="I79" s="17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F80" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="G80" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="H80" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="I80" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E81" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F81" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G81" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="H81" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I81" s="19" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E82" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="G82" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="H82" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E83" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I83" s="19"/>
+    </row>
+    <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E84" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="G84" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="H84" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I84" s="19"/>
+    </row>
+    <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E85" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="H85" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I85" s="19"/>
+    </row>
+    <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E86" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H86" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I86" s="17" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I78"/>
-  <conditionalFormatting sqref="A2:I78">
+  <autoFilter ref="A1:I86"/>
+  <conditionalFormatting sqref="A2:I86">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H2="구간 이동"</formula>
     </cfRule>
@@ -8067,7 +8869,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H78" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H86" type="list">
       <formula1>"유지,구간 이동,추가,신규,탭 밖 이동"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/관심종목/09_SW_구간표준.xlsx
+++ b/관심종목/09_SW_구간표준.xlsx
@@ -14,7 +14,7 @@
     <sheet name="종목 목록" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'종목 목록'!$A$1:$I$86</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'종목 목록'!$A$1:$I$91</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="367">
   <si>
     <r>
       <rPr>
@@ -886,7 +886,82 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">트렌드마이크로</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트렌드마이크로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사이버시큐리티클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">글로벌시큐리티엑스퍼트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">브로드밴드시큐리티</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">벌크홀딩스</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">양자</t>
@@ -1099,7 +1174,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">–</t>
+    <t xml:space="preserve">핏쿠스타즈</t>
   </si>
   <si>
     <t xml:space="preserve">게임</t>
@@ -2283,7 +2358,161 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">메모로 양자 표시 </t>
+      <t xml:space="preserve">메모로 양자 표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 구간으로 옮겨도 됨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소프트뱅크그룹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스퀘어</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탭에 넣지 않음</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">투자형 지주사</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금융 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자산운용 투자 구간에 추가</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">코어위브</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월가 탭에 유지</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
     </r>
     <r>
       <rPr>
@@ -2300,7 +2529,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">같은 탭이라 함께 보임</t>
+      <t xml:space="preserve">네오클라우드</t>
     </r>
     <r>
       <rPr>
@@ -2316,95 +2545,19 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">소프트뱅크그룹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스퀘어</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">국장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탭에 넣지 않음</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">투자형 지주사</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터센터 </t>
     </r>
     <r>
       <rPr>
@@ -2421,32 +2574,44 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">자산운용 투자 구간에 추가</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">코어위브</t>
-  </si>
-  <si>
-    <t xml:space="preserve">월가 탭에 유지</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
+      <t xml:space="preserve">서버 랙 후보</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일장 신규 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종목 코드</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추가 </t>
     </r>
     <r>
       <rPr>
@@ -2463,7 +2628,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">네오클라우드</t>
+      <t xml:space="preserve">코드 미검증</t>
     </r>
     <r>
       <rPr>
@@ -2479,105 +2644,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터센터 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서버 랙 후보</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일장 신규 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종목 코드</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">추가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">코드 미검증</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -2633,6 +2699,74 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">트렌드마이크로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사이버시큐리티클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">글로벌시큐리티엑스퍼트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">브로드밴드시큐리티</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">벌크홀딩스</t>
     </r>
     <r>
       <rPr>
@@ -2738,7 +2872,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">빈칸메모 입력 순서</t>
+      <t xml:space="preserve">빈칸메모 입력 순서 </t>
     </r>
     <r>
       <rPr>
@@ -2748,7 +2882,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -2757,7 +2891,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">플랫폼 </t>
+      <t xml:space="preserve">세 시장 공통</t>
     </r>
     <r>
       <rPr>
@@ -2767,7 +2901,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/ SaaS IT</t>
+      <t xml:space="preserve">): </t>
     </r>
     <r>
       <rPr>
@@ -2776,7 +2910,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">서비스 </t>
+      <t xml:space="preserve">플랫폼 </t>
     </r>
     <r>
       <rPr>
@@ -2786,7 +2920,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/ AI </t>
+      <t xml:space="preserve">/ SaaS IT</t>
     </r>
     <r>
       <rPr>
@@ -2795,7 +2929,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">소프트웨어 </t>
+      <t xml:space="preserve">서비스 </t>
     </r>
     <r>
       <rPr>
@@ -2805,7 +2939,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/ </t>
+      <t xml:space="preserve">/ AI </t>
     </r>
     <r>
       <rPr>
@@ -2814,7 +2948,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">보안 </t>
+      <t xml:space="preserve">소프트웨어 </t>
     </r>
     <r>
       <rPr>
@@ -2833,7 +2967,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">양자 </t>
+      <t xml:space="preserve">보안 </t>
     </r>
     <r>
       <rPr>
@@ -2852,7 +2986,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">게임 </t>
+      <t xml:space="preserve">양자 </t>
     </r>
     <r>
       <rPr>
@@ -2862,7 +2996,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">/ </t>
     </r>
     <r>
       <rPr>
@@ -2871,12 +3005,70 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일장은 양자 구간 없음</t>
-    </r>
+      <t xml:space="preserve">게임</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">구간 순서</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원래 위치 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탭 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구간</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2885,9 +3077,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">구간 순서</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -2896,7 +3085,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원래 위치 </t>
+      <t xml:space="preserve">종목코드</t>
     </r>
     <r>
       <rPr>
@@ -2907,23 +3096,843 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">티커</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">영웅문 코드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메모</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">035420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구간 이동</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금융 탭에서 빼고 여기로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탭 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구글</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메타 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">카카오</t>
+  </si>
+  <si>
+    <t xml:space="preserve">035720</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신규 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신규</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사람인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">신규</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구인 플랫폼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리크루트 짝</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sw / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보안</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">삼성에스디에스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">018260</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서비스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">가비아</t>
+  </si>
+  <si>
+    <t xml:space="preserve">079940</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">호스팅</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">케이아이엔엑스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">093320</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인터넷 연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(IX), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가비아 자회사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">솔트룩스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304100</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">언어모델</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팔란티어 테마 연동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">코난테크놀로지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402030</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">언어모델</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">윈스테크넷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안랩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">053800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엑스게이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">025770</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VAN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업체</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">150900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에스투더블유</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">드림시큐리티</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라온시큐어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">042510</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sw / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">아이씨티케이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">456010</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자암호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자통신</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">옵티시스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">우리넷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">046970</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자암호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터센터 탭 광부품과 중복</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">코위버</t>
+  </si>
+  <si>
+    <t xml:space="preserve">056360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">쏠리드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">050890</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sw / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게임</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">036570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">크래프톤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">259960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">펄어비스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위메이드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">컴투스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">078340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">넷마블</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">넥슨게임즈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225570</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">넥슨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일본 상장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개발 자회사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">060250</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금융</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핀테크로 이동 완료</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">234340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">064260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">054920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">064400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">053300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">041190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">462860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307950</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동차 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2932,19 +3941,170 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구간</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자율주행으로 이동 예정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">298830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118990</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월가 포트폴리오 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">드러켄밀러</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">아마존닷컴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMZN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDAMZN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월가 탭과 의도적 중복</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마이크로소프트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDMSFT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">애저 클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빅테크</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알파벳 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDGOOGL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAVER </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">짝</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메타 플랫폼스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">페이스북</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2953,64 +4113,429 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종목코드</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">티커</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">영웅문 코드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상태</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메모</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAVER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">035420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구간 이동</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융 탭에서 빼고 여기로 </t>
+    <t xml:space="preserve">META</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDMETA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카카오 짝</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미국 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sw / SaaS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">브로드리지 파이낸셜 솔루션</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYBR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금융 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SW</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">피그마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYFIG</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디자인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SaaS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYNOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">헬스케어 탭에서 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDWDAY</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">헬스케어 탭에서 이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, HR SaaS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYCRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDINTU</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">new </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탭에서 이동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DDOG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDDDOG</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모니터링 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SW, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정책 수혜주 탭에서 이동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">오라클</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYORCL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터센터 수요</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">팔란티어 테크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDPLTR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI SW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">테마 선행 신호</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CRWD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDCRWD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정책 수혜주 탭에서 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDPANW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDOKTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IONQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYIONQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">데이터센터 탭에서 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDLAES</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자내성 보안칩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국장 양자암호 짝</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RGTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRGTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QTUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDQTUM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ETF</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">QBTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDQBTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDQUBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYINFQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로블록스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBLX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYRBLX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">테이크 투 인터랙티브 소프트웨어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTWO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDTTWO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크래프톤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">펄어비스 짝 </t>
     </r>
     <r>
       <rPr>
@@ -3027,7 +4552,505 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구글</t>
+      <t xml:space="preserve">콘솔 대작</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">리크루트홀딩스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06098</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인디드 운영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사람인 짝</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">코퍼레이션</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">04689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04689</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라인야후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, NAVER·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카카오 짝</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">06701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06701</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일본 테마 탭에서 이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">삼성에스디에스 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자컴퓨터 개발 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 구간 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">해저케이블</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">06702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06702</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일본 테마 탭에서 이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">삼성에스디에스 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자컴퓨터 개발 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 구간 짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">03778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W03778</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">트렌드마이크로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안랩 짝</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사이버시큐리티클라우드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04493</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">웹방화벽 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WAF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클라우드플레어 짝</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">글로벌시큐리티엑스퍼트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04417</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보안 컨설팅 교육</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중소기업 대상</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">브로드밴드시큐리티</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">취약점 진단 보안감사 관제</t>
+  </si>
+  <si>
+    <t xml:space="preserve">벌크홀딩스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W02467</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본업 마케팅 리서치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자회사 보안 교육 컨설팅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">테마성</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">03687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W03687</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일본 테마 탭에서 이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양자 최적화 클라우드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Amplify), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아이온큐</t>
     </r>
     <r>
       <rPr>
@@ -3044,1683 +5067,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">메타 짝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">카카오</t>
-  </si>
-  <si>
-    <t xml:space="preserve">035720</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신규 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신규</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">사람인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">신규</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구인 플랫폼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">리크루트 짝</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sw / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보안</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">삼성에스디에스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">018260</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서비스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">가비아</t>
-  </si>
-  <si>
-    <t xml:space="preserve">079940</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">호스팅</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">케이아이엔엑스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">093320</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인터넷 연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(IX), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가비아 자회사</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">솔트룩스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304100</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">언어모델</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">팔란티어 테마 연동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">코난테크놀로지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402030</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">검색</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">언어모델</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">윈스테크넷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">유지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">안랩</t>
-  </si>
-  <si>
-    <t xml:space="preserve">053800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엑스게이트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">025770</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VAN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">업체</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">150900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">에스투더블유</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">드림시큐리티</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">라온시큐어</t>
-  </si>
-  <si>
-    <t xml:space="preserve">042510</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sw / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">아이씨티케이</t>
-  </si>
-  <si>
-    <t xml:space="preserve">456010</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자암호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자통신</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">옵티시스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">우리넷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">046970</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자암호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터센터 탭 광부품과 중복</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">코위버</t>
-  </si>
-  <si>
-    <t xml:space="preserve">056360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">쏠리드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">050890</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sw / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게임</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">036570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">크래프톤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">259960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">펄어비스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">위메이드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">컴투스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">078340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">넷마블</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">넥슨게임즈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225570</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">넥슨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일본 상장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개발 자회사</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">060250</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">핀테크로 이동 완료</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">234340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">064260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">054920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">064400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">053300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">041190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">377300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">462860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307950</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">05 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로봇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자동차 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자율주행으로 이동 예정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">298830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118990</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">월가 포트폴리오 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">드러켄밀러</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">아마존닷컴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDAMZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">월가 탭과 의도적 중복</t>
-  </si>
-  <si>
-    <t xml:space="preserve">마이크로소프트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSFT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDMSFT</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">애저 클라우드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빅테크</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알파벳 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">GOOGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDGOOGL</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAVER </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">짝</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메타 플랫폼스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">페이스북</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">META</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDMETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">카카오 짝</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미국 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sw / SaaS</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">브로드리지 파이낸셜 솔루션</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYBR</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SW</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">피그마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYFIG</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디자인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SaaS</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYNOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">헬스케어 탭에서 이동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDWDAY</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">헬스케어 탭에서 이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, HR SaaS</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYCRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDINTU</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">new </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탭에서 이동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">DDOG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDDDOG</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모니터링 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SW, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정책 수혜주 탭에서 이동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">오라클</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYORCL</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터센터 수요</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">팔란티어 테크</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLTR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDPLTR</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">국장 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI SW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">테마 선행 신호</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CRWD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDCRWD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정책 수혜주 탭에서 이동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDPANW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OKTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDOKTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IONQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYIONQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">데이터센터 탭에서 이동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDLAES</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자내성 보안칩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">국장 양자암호 짝</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">RGTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDRGTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QTUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDQTUM</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ETF</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">QBTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDQBTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUBT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDQUBT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RIME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDRIME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYINFQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">로블록스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBLX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYRBLX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">테이크 투 인터랙티브 소프트웨어</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTWO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDTTWO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">크래프톤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">펄어비스 짝 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">콘솔 대작</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">리크루트홀딩스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06098</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인디드 운영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사람인 짝</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">코퍼레이션</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">04689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W04689</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">라인야후</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, NAVER·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카카오 짝</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">06701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06701</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일본 테마 탭에서 이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">삼성에스디에스 짝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자컴퓨터 개발 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자 구간 짝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">해저케이블</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">06702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06702</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일본 테마 탭에서 이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">삼성에스디에스 짝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자컴퓨터 개발 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양자 구간 짝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">03778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W03778</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클라우드</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">04704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W04704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">안랩 짝</t>
+      <t xml:space="preserve">디웨이브 짝</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">닌텐도</t>
@@ -5443,15 +5791,15 @@
         <v>10</v>
       </c>
       <c r="C5" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B5,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"국장",'종목 목록'!$C$2:$C$91,$B5,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B5,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"미장",'종목 목록'!$C$2:$C$91,$B5,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B5,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"일장",'종목 목록'!$C$2:$C$91,$B5,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -5472,15 +5820,15 @@
         <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B6,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"국장",'종목 목록'!$C$2:$C$91,$B6,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B6,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"미장",'종목 목록'!$C$2:$C$91,$B6,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B6,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"일장",'종목 목록'!$C$2:$C$91,$B6,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -5501,15 +5849,15 @@
         <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B7,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"국장",'종목 목록'!$C$2:$C$91,$B7,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B7,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"미장",'종목 목록'!$C$2:$C$91,$B7,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B7,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"일장",'종목 목록'!$C$2:$C$91,$B7,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -5522,7 +5870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
@@ -5530,16 +5878,16 @@
         <v>22</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B8,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"국장",'종목 목록'!$C$2:$C$91,$B8,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B8,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"미장",'종목 목록'!$C$2:$C$91,$B8,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B8,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"일장",'종목 목록'!$C$2:$C$91,$B8,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
+        <v>5</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>23</v>
@@ -5559,16 +5907,16 @@
         <v>26</v>
       </c>
       <c r="C9" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B9,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"국장",'종목 목록'!$C$2:$C$91,$B9,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B9,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"미장",'종목 목록'!$C$2:$C$91,$B9,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B9,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"일장",'종목 목록'!$C$2:$C$91,$B9,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
+        <v>1</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>27</v>
@@ -5576,7 +5924,7 @@
       <c r="G9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5588,15 +5936,15 @@
         <v>30</v>
       </c>
       <c r="C10" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"국장",'종목 목록'!$C$2:$C$86,$B10,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"국장",'종목 목록'!$C$2:$C$91,$B10,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"미장",'종목 목록'!$C$2:$C$86,$B10,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"미장",'종목 목록'!$C$2:$C$91,$B10,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$86,"일장",'종목 목록'!$C$2:$C$86,$B10,'종목 목록'!$H$2:$H$86,"&lt;&gt;탭 밖 이동")</f>
+        <f aca="false">COUNTIFS('종목 목록'!$A$2:$A$91,"일장",'종목 목록'!$C$2:$C$91,$B10,'종목 목록'!$H$2:$H$91,"&lt;&gt;탭 밖 이동")</f>
         <v>4</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -5623,7 +5971,7 @@
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">SUM(E5:E10)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5642,7 +5990,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -6200,6 +6548,20 @@
       </c>
       <c r="D41" s="14" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -6380,7 +6742,7 @@
       </c>
       <c r="F10" s="15"/>
     </row>
-    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
         <v>125</v>
       </c>
@@ -6419,7 +6781,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -8727,19 +9089,19 @@
         <v>142</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>25</v>
+        <v>331</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>145</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8747,114 +9109,259 @@
         <v>6</v>
       </c>
       <c r="B83" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D83" s="17" t="s">
         <v>142</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="I83" s="19"/>
+      <c r="I83" s="17" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B84" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D84" s="17" t="s">
         <v>142</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="I84" s="19"/>
+      <c r="I84" s="17" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B85" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D85" s="17" t="s">
         <v>142</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="I85" s="19"/>
+      <c r="I85" s="17" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B86" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D86" s="17" t="s">
         <v>142</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>145</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>346</v>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D87" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E87" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="H87" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="I87" s="17" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E88" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="H88" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I88" s="19"/>
+    </row>
+    <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E89" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="F89" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="G89" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="H89" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I89" s="19"/>
+    </row>
+    <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E90" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="F90" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="G90" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="H90" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I90" s="19"/>
+    </row>
+    <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D91" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E91" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="G91" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="H91" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I91" s="17" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I86"/>
-  <conditionalFormatting sqref="A2:I86">
+  <autoFilter ref="A1:I91"/>
+  <conditionalFormatting sqref="A2:I91">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H2="구간 이동"</formula>
     </cfRule>
@@ -8869,7 +9376,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H86" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H91" type="list">
       <formula1>"유지,구간 이동,추가,신규,탭 밖 이동"</formula1>
       <formula2>0</formula2>
     </dataValidation>
